--- a/data/cox_xlsx/CHEMM.CO.xlsx
+++ b/data/cox_xlsx/CHEMM.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="371">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>Lease liabilities</t>
+  </si>
+  <si>
+    <t>Bank Loans LT</t>
   </si>
   <si>
     <t>Deferred Tax - Credit - Liability</t>
@@ -1254,7 +1257,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1332,6 +1335,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11676,8 +11682,8 @@
       <c r="V89" s="17"/>
     </row>
     <row r="90" ht="15.0" customHeight="1">
-      <c r="A90" s="14" t="s">
-        <v>215</v>
+      <c r="A90" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -11717,7 +11723,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B91" s="17">
         <v>0.0</v>
@@ -11757,7 +11763,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B92" s="17">
         <v>0.0</v>
@@ -11785,7 +11791,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B93" s="20">
         <v>12.22</v>
@@ -11853,7 +11859,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B94" s="22">
         <v>0.0</v>
@@ -11883,7 +11889,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B95" s="19">
         <v>245.55</v>
@@ -11951,7 +11957,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B96" s="16">
         <v>27.62</v>
@@ -12019,7 +12025,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B97" s="15">
         <v>1041.25</v>
@@ -12057,7 +12063,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B98" s="21">
         <v>-13.88</v>
@@ -12101,7 +12107,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B99" s="15">
         <v>861.76</v>
@@ -12169,7 +12175,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -12197,7 +12203,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B101" s="15">
         <v>193.37</v>
@@ -12237,7 +12243,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B102" s="19">
         <v>1068.87</v>
@@ -12305,7 +12311,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B103" s="19">
         <v>1068.87</v>
@@ -12373,7 +12379,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B104" s="17">
         <v>0.0</v>
@@ -12401,7 +12407,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B105" s="19">
         <v>1314.43</v>
@@ -12469,7 +12475,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B106" s="16">
         <v>17.4</v>
@@ -12537,7 +12543,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B107" s="16">
         <v>17.4</v>
@@ -12605,7 +12611,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B108" s="17">
         <v>0.0</v>
@@ -12673,7 +12679,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B109" s="16">
         <v>7.84</v>
@@ -12715,7 +12721,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B110" s="16">
         <v>3.05</v>
@@ -12757,7 +12763,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B111" s="16">
         <v>4.07</v>
@@ -12799,7 +12805,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B112" s="16">
         <v>0.72</v>
@@ -12841,7 +12847,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
@@ -12869,7 +12875,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
@@ -12897,7 +12903,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
@@ -12925,7 +12931,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
@@ -12953,7 +12959,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
@@ -12981,7 +12987,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -13009,7 +13015,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
@@ -13037,7 +13043,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -13071,7 +13077,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
@@ -13103,7 +13109,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B122" s="16">
         <v>17.4</v>
@@ -13171,7 +13177,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B123" s="17">
         <v>0.0</v>
@@ -13239,7 +13245,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B124" s="16">
         <v>1.0</v>
@@ -13307,7 +13313,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B125" s="16">
         <v>17.4</v>
@@ -13375,7 +13381,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
@@ -13421,7 +13427,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
@@ -13461,7 +13467,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
@@ -13501,7 +13507,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
@@ -13541,7 +13547,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
@@ -13575,7 +13581,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B131" s="17">
         <v>17031.0</v>
@@ -14520,7 +14526,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14893,67 +14899,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15026,7 +15032,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15120,7 +15126,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B20" s="15">
         <v>371.02</v>
@@ -15188,7 +15194,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B21" s="16">
         <v>33.78</v>
@@ -15256,7 +15262,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -15298,7 +15304,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B23" s="21">
         <v>-66.72</v>
@@ -15340,7 +15346,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B24" s="16">
         <v>9.25</v>
@@ -15392,7 +15398,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B25" s="21">
         <v>-0.94</v>
@@ -15460,7 +15466,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B26" s="21">
         <v>-20.96</v>
@@ -15512,7 +15518,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -15556,7 +15562,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -15600,7 +15606,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -15644,7 +15650,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -15672,7 +15678,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" s="19">
         <v>325.43</v>
@@ -15740,7 +15746,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" s="21">
         <v>-46.85</v>
@@ -15808,7 +15814,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" s="21">
         <v>-54.7</v>
@@ -15876,7 +15882,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -15914,7 +15920,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
@@ -15960,7 +15966,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" s="17">
         <v>0.0</v>
@@ -16008,7 +16014,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B37" s="17">
         <v>0.0</v>
@@ -16040,7 +16046,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -16080,7 +16086,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" s="21">
         <v>-32.61</v>
@@ -16108,7 +16114,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -16140,9 +16146,9 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="B41" s="26">
+        <v>297</v>
+      </c>
+      <c r="B41" s="27">
         <v>-134.16</v>
       </c>
       <c r="C41" s="23">
@@ -16208,7 +16214,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B42" s="21">
         <v>-0.76</v>
@@ -16276,7 +16282,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B43" s="21">
         <v>-8.47</v>
@@ -16336,7 +16342,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B44" s="25">
         <v>-109.18</v>
@@ -16374,7 +16380,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
@@ -16404,7 +16410,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -16436,7 +16442,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -16474,7 +16480,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -16512,7 +16518,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -16540,7 +16546,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B50" s="16">
         <v>0.82</v>
@@ -16570,7 +16576,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -16600,7 +16606,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -16640,7 +16646,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B53" s="17">
         <v>0.0</v>
@@ -16674,7 +16680,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -16702,12 +16708,12 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B55" s="26">
+        <v>311</v>
+      </c>
+      <c r="B55" s="27">
         <v>-117.59</v>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <v>-163.06</v>
       </c>
       <c r="D55" s="23">
@@ -16770,7 +16776,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B56" s="21">
         <v>-1.98</v>
@@ -16826,7 +16832,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B57" s="15">
         <v>470.1</v>
@@ -16894,7 +16900,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B58" s="15">
         <v>542.65</v>
@@ -16962,7 +16968,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B59" s="16">
         <v>73.68</v>
@@ -17014,7 +17020,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -17042,7 +17048,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B61" s="20">
         <v>71.69</v>
@@ -18069,7 +18075,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18575,7 +18581,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -18668,2526 +18674,2526 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
+      <c r="A20" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>319</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" s="31">
         <v>15614.0</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>7674.66</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>12253.11</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>17998.98</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>19928.93</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>7809.03</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>3261.3</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>1289.32</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>694.97</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>701.64</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>328.28</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>63.61</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>61.6</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>62.38</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>76.63</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>84.82</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>239.52</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>381.62</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>273.68</v>
       </c>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B22" s="31">
         <v>15920.82</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>14004.25</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>13572.15</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>10104.03</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>6577.27</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>2901.99</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>1274.55</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>625.79</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>384.44</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>254.36</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>124.06</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>74.05</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>99.5</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>155.52</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>201.22</v>
       </c>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>321</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
+      <c r="A23" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>321</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="31">
         <v>16146.48</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>8122.06</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>12739.15</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>18279.59</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>20131.56</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>7946.23</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>3364.51</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>1276.13</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>682.84</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>691.51</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>331.86</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>69.35</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>68.5</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>67.78</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>79.78</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>89.16</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>248.2</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>387.43</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>291.46</v>
       </c>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B25" s="31">
         <v>16329.35</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>14324.8</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>13834.0</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>10246.6</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>6660.11</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>2944.36</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>1288.73</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>620.75</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>383.69</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>257.33</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>129.45</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>79.46</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>105.02</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>160.58</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>208.81</v>
       </c>
-      <c r="Q25" s="30"/>
-      <c r="R25" s="30"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="B27" s="32">
         <v>927.83</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>466.72</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>732.03</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>1050.4</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>1156.82</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>456.61</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>193.33</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>73.33</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>39.24</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>39.74</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>19.07</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>3.98</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>3.94</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>3.89</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>4.58</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="33">
         <v>5.12</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="33">
         <v>14.26</v>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="33">
         <v>22.26</v>
       </c>
-      <c r="T27" s="32">
+      <c r="T27" s="33">
         <v>16.75</v>
       </c>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>325</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" s="32">
         <v>938.33</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>823.15</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>794.94</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>588.8</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>382.71</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>169.19</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>74.05</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>35.67</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>22.05</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>14.79</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="33">
         <v>7.44</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="33">
         <v>4.57</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <v>6.03</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <v>9.23</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>12.0</v>
       </c>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>326</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
+      <c r="A29" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="B30" s="34">
         <v>1.4</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>1.61</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>1.4</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>0.92</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>0.57</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>1.02</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>1.35</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>1.01</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>-0.17</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>-2.55</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>1.73</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>-2.36</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>1.81</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>3.27</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>-1.32</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>-3.68</v>
       </c>
-      <c r="R30" s="33">
+      <c r="R30" s="34">
         <v>0.84</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>-2.86</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>-3.52</v>
       </c>
-      <c r="U30" s="33"/>
-      <c r="V30" s="33"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" s="34">
         <v>1.06</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>0.98</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>0.93</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>0.83</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>0.75</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>0.84</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>0.7</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>-0.06</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>-0.7</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>-0.71</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>1.05</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>-0.62</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="34">
         <v>0.2</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>-1.32</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>-2.23</v>
       </c>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="33"/>
-      <c r="V31" s="33"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>329</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
+      <c r="A32" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>330</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" s="34">
         <v>0.68</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>1.97</v>
       </c>
-      <c r="D33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="33">
+      <c r="D33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="34">
         <v>0.53</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>0.18</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>2.38</v>
       </c>
-      <c r="H33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="S33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="T33" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
+      <c r="H33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="S33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="T33" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U33" s="34"/>
+      <c r="V33" s="34"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" s="34">
         <v>0.52</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>0.71</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <v>0.51</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <v>0.61</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>0.65</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <v>1.29</v>
       </c>
-      <c r="H34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
+      <c r="H34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>332</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="B35" s="34">
         <v>0.68</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>1.97</v>
       </c>
-      <c r="D35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="33">
+      <c r="D35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="34">
         <v>0.53</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>0.18</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>2.38</v>
       </c>
-      <c r="H35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="R35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="S35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="T35" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="U35" s="33"/>
-      <c r="V35" s="33"/>
+      <c r="H35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="R35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="S35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="T35" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="U35" s="34"/>
+      <c r="V35" s="34"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="34">
         <v>0.52</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>0.71</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <v>0.51</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <v>0.61</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>0.65</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <v>1.29</v>
       </c>
-      <c r="H36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="33">
-        <v>0.0</v>
-      </c>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
+      <c r="H36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="34">
+        <v>0.0</v>
+      </c>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>334</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
+      <c r="A37" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>335</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="B38" s="33">
         <v>15.11</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>9.38</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>15.21</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>36.88</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>55.4</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>27.04</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>13.52</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>12.08</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>7.45</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>8.77</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>5.51</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>1.38</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>1.49</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>1.56</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>1.44</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>1.58</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>3.63</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>6.97</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>6.91</v>
       </c>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="31"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="B39" s="33">
         <v>21.49</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>24.3</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>28.42</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>33.59</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>29.85</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>16.61</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>10.77</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>7.76</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>5.46</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>4.2</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>2.35</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>1.49</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>2.0</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>3.09</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>3.94</v>
       </c>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="31"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>337</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
+      <c r="A40" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>338</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="B41" s="33">
         <v>19.55</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>11.26</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>17.89</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>45.46</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>70.88</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>36.21</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>18.28</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>25.35</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>13.97</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>16.27</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>11.23</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>3.01</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>3.24</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>3.22</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>4.17</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>3.97</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>6.51</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>10.03</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>8.38</v>
       </c>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B42" s="33">
         <v>26.49</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>29.73</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>35.42</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>44.52</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>42.04</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>25.1</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>17.8</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>15.45</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>10.85</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>8.55</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>5.28</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>3.51</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>4.45</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>6.21</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>7.16</v>
       </c>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
+      <c r="A43" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>341</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="B44" s="33">
         <v>20.53</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>13.0</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>18.25</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>30.75</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>52.21</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>24.8</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>13.19</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>7.91</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>5.31</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>5.85</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>4.17</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>1.36</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>1.56</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>1.7</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>2.04</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>2.56</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>6.38</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>8.04</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>11.38</v>
       </c>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
+      <c r="U44" s="31"/>
+      <c r="V44" s="31"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>342</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="B45" s="33">
         <v>25.0</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>26.22</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>28.02</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>29.46</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>26.25</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>13.75</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>8.46</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>5.59</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>4.28</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>3.57</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>2.39</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>1.8</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>2.71</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>4.25</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>5.84</v>
       </c>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
+      <c r="S45" s="31"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>343</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
+      <c r="A46" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>344</v>
-      </c>
-      <c r="B47" s="32">
+      <c r="A47" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B47" s="33">
         <v>71.27</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <v>62.02</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="33">
         <v>71.56</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>108.92</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>176.26</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <v>98.52</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <v>74.07</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="33">
         <v>99.3</v>
       </c>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="32">
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="33">
         <v>57.9</v>
       </c>
-      <c r="M47" s="30"/>
-      <c r="N47" s="32">
+      <c r="M47" s="31"/>
+      <c r="N47" s="33">
         <v>55.11</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="33">
         <v>30.62</v>
       </c>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="31">
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="32">
         <v>118.77</v>
       </c>
-      <c r="S47" s="30"/>
-      <c r="T47" s="30"/>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
+      <c r="S47" s="31"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>345</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="B48" s="33">
         <v>94.25</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>101.91</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <v>107.89</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <v>121.11</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <v>132.68</v>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <v>118.6</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="32">
         <v>142.11</v>
       </c>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="32">
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="33">
         <v>95.4</v>
       </c>
-      <c r="M48" s="30"/>
-      <c r="N48" s="31">
+      <c r="M48" s="31"/>
+      <c r="N48" s="32">
         <v>492.7</v>
       </c>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="S48" s="30"/>
-      <c r="T48" s="30"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="31"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="31"/>
+      <c r="V48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>346</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
+      <c r="A49" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B50" s="33">
         <v>48.92</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>34.43</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>40.74</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>73.35</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>138.29</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>71.19</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>43.91</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>37.12</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>36.43</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>28.97</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L50" s="33">
         <v>18.88</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M50" s="33">
         <v>8.91</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="33">
         <v>9.92</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>6.31</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>10.3</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>30.83</v>
       </c>
-      <c r="R50" s="32">
+      <c r="R50" s="33">
         <v>29.36</v>
       </c>
-      <c r="S50" s="32">
+      <c r="S50" s="33">
         <v>24.73</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>136.11</v>
       </c>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
+      <c r="U50" s="31"/>
+      <c r="V50" s="31"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="B51" s="32">
+      <c r="A51" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="B51" s="33">
         <v>60.75</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <v>65.31</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <v>70.93</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <v>82.3</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <v>85.6</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <v>51.65</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <v>36.83</v>
       </c>
-      <c r="I51" s="32">
+      <c r="I51" s="33">
         <v>29.43</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="33">
         <v>24.06</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="33">
         <v>17.71</v>
       </c>
-      <c r="L51" s="32">
+      <c r="L51" s="33">
         <v>11.9</v>
       </c>
-      <c r="M51" s="32">
+      <c r="M51" s="33">
         <v>10.34</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="33">
         <v>14.5</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="33">
         <v>18.74</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>29.62</v>
       </c>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
+      <c r="A52" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="B53" s="32">
+      <c r="A53" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B53" s="33">
         <v>54.57</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>38.9</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>45.39</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>82.61</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>166.14</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <v>89.75</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <v>55.31</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="33">
         <v>48.92</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="33">
         <v>64.05</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>47.57</v>
       </c>
-      <c r="L53" s="32">
+      <c r="L53" s="33">
         <v>32.11</v>
       </c>
-      <c r="M53" s="32">
+      <c r="M53" s="33">
         <v>53.46</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>186.68</v>
       </c>
-      <c r="O53" s="30"/>
-      <c r="P53" s="31">
+      <c r="O53" s="31"/>
+      <c r="P53" s="32">
         <v>703.81</v>
       </c>
-      <c r="Q53" s="30"/>
-      <c r="R53" s="32">
+      <c r="Q53" s="31"/>
+      <c r="R53" s="33">
         <v>44.46</v>
       </c>
-      <c r="S53" s="32">
+      <c r="S53" s="33">
         <v>27.24</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>223.26</v>
       </c>
-      <c r="U53" s="30"/>
-      <c r="V53" s="30"/>
+      <c r="U53" s="31"/>
+      <c r="V53" s="31"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="B54" s="32">
+      <c r="A54" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="B54" s="33">
         <v>68.65</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <v>74.93</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>82.4</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>98.16</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>107.93</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>68.5</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>51.63</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>48.26</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>49.4</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>85.29</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>1009.99</v>
       </c>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="31">
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="32">
         <v>181.42</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>64.45</v>
       </c>
-      <c r="Q54" s="30"/>
-      <c r="R54" s="30"/>
-      <c r="S54" s="30"/>
-      <c r="T54" s="30"/>
-      <c r="U54" s="30"/>
-      <c r="V54" s="30"/>
+      <c r="Q54" s="31"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+      <c r="U54" s="31"/>
+      <c r="V54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
+      <c r="A55" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="B56" s="33">
         <v>46.13</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>38.9</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>45.39</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>82.61</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>163.8</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <v>89.75</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <v>55.31</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>48.92</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>64.05</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>47.57</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="33">
         <v>32.11</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>53.46</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>186.68</v>
       </c>
-      <c r="O56" s="30"/>
-      <c r="P56" s="31">
+      <c r="O56" s="31"/>
+      <c r="P56" s="32">
         <v>703.81</v>
       </c>
-      <c r="Q56" s="30"/>
-      <c r="R56" s="32">
+      <c r="Q56" s="31"/>
+      <c r="R56" s="33">
         <v>44.46</v>
       </c>
-      <c r="S56" s="32">
+      <c r="S56" s="33">
         <v>27.24</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>223.26</v>
       </c>
-      <c r="U56" s="30"/>
-      <c r="V56" s="30"/>
+      <c r="U56" s="31"/>
+      <c r="V56" s="31"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="B57" s="32">
+      <c r="A57" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="B57" s="33">
         <v>21.49</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>24.3</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>28.42</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="33">
         <v>33.59</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <v>29.85</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>16.61</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <v>10.77</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>7.76</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="33">
         <v>5.46</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="33">
         <v>4.2</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="33">
         <v>2.35</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="33">
         <v>1.49</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="33">
         <v>2.0</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="33">
         <v>3.09</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>3.94</v>
       </c>
-      <c r="Q57" s="30"/>
-      <c r="R57" s="30"/>
-      <c r="S57" s="30"/>
-      <c r="T57" s="30"/>
-      <c r="U57" s="30"/>
-      <c r="V57" s="30"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
+      <c r="A58" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="B59" s="32">
+      <c r="A59" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59" s="33">
         <v>1.48</v>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="36">
         <v>-1.64</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="33">
         <v>3.77</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <v>1.03</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="33">
         <v>3.72</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <v>2.94</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <v>0.43</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="33">
         <v>0.34</v>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="36">
         <v>-2.24</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="33">
         <v>1.49</v>
       </c>
-      <c r="L59" s="32">
+      <c r="L59" s="33">
         <v>0.05</v>
       </c>
-      <c r="M59" s="32">
+      <c r="M59" s="33">
         <v>0.23</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="33">
         <v>1.8</v>
       </c>
-      <c r="O59" s="30"/>
-      <c r="P59" s="32">
+      <c r="O59" s="31"/>
+      <c r="P59" s="33">
         <v>6.84</v>
       </c>
-      <c r="Q59" s="30"/>
-      <c r="R59" s="35">
+      <c r="Q59" s="31"/>
+      <c r="R59" s="36">
         <v>-0.68</v>
       </c>
-      <c r="S59" s="32">
+      <c r="S59" s="33">
         <v>0.03</v>
       </c>
-      <c r="T59" s="35">
+      <c r="T59" s="36">
         <v>-3.15</v>
       </c>
-      <c r="U59" s="30"/>
-      <c r="V59" s="30"/>
+      <c r="U59" s="31"/>
+      <c r="V59" s="31"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="B60" s="32">
+      <c r="A60" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="B60" s="33">
         <v>2.75</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="33">
         <v>3.14</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="33">
         <v>1.52</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="33">
         <v>1.22</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="33">
         <v>2.16</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="33">
         <v>1.45</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="33">
         <v>0.47</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="33">
         <v>0.38</v>
       </c>
-      <c r="J60" s="30"/>
-      <c r="K60" s="32">
+      <c r="J60" s="31"/>
+      <c r="K60" s="33">
         <v>0.55</v>
       </c>
-      <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="30"/>
-      <c r="O60" s="30"/>
-      <c r="P60" s="35">
+      <c r="L60" s="31"/>
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="36">
         <v>-1.24</v>
       </c>
-      <c r="Q60" s="30"/>
-      <c r="R60" s="30"/>
-      <c r="S60" s="30"/>
-      <c r="T60" s="30"/>
-      <c r="U60" s="30"/>
-      <c r="V60" s="30"/>
+      <c r="Q60" s="31"/>
+      <c r="R60" s="31"/>
+      <c r="S60" s="31"/>
+      <c r="T60" s="31"/>
+      <c r="U60" s="31"/>
+      <c r="V60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>358</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
+      <c r="A61" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="B62" s="33">
         <v>19.85</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>12.28</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>17.55</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>30.28</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>51.69</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>25.16</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>14.3</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>8.96</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>6.0</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>6.59</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>4.58</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>1.25</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>1.41</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>1.57</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>1.97</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>2.44</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>6.17</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>7.92</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>11.45</v>
       </c>
-      <c r="U62" s="30"/>
-      <c r="V62" s="30"/>
+      <c r="U62" s="31"/>
+      <c r="V62" s="31"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="B63" s="33">
         <v>24.37</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>25.73</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>27.99</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>30.04</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>27.44</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>14.77</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>9.34</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>6.21</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>4.63</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>3.74</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>2.36</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>1.68</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>2.58</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>4.12</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>5.68</v>
       </c>
-      <c r="Q63" s="30"/>
-      <c r="R63" s="30"/>
-      <c r="S63" s="30"/>
-      <c r="T63" s="30"/>
-      <c r="U63" s="30"/>
-      <c r="V63" s="30"/>
+      <c r="Q63" s="31"/>
+      <c r="R63" s="31"/>
+      <c r="S63" s="31"/>
+      <c r="T63" s="31"/>
+      <c r="U63" s="31"/>
+      <c r="V63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
+      <c r="A64" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="29"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="B65" s="33">
         <v>36.45</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>26.83</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>31.07</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>58.2</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>107.92</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>58.17</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>38.67</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>33.58</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>33.67</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>24.83</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="33">
         <v>24.6</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>7.64</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>7.63</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>6.87</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>9.09</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>16.45</v>
       </c>
-      <c r="R65" s="32">
+      <c r="R65" s="33">
         <v>44.66</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>22.04</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>118.28</v>
       </c>
-      <c r="U65" s="30"/>
-      <c r="V65" s="30"/>
+      <c r="U65" s="31"/>
+      <c r="V65" s="31"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="B66" s="33">
         <v>47.08</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>51.47</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>56.39</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>66.79</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>70.88</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>44.23</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>33.8</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>27.98</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>23.01</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>17.56</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>12.2</v>
       </c>
-      <c r="M66" s="32">
+      <c r="M66" s="33">
         <v>8.92</v>
       </c>
-      <c r="N66" s="32">
+      <c r="N66" s="33">
         <v>13.87</v>
       </c>
-      <c r="O66" s="32">
+      <c r="O66" s="33">
         <v>18.1</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>27.0</v>
       </c>
-      <c r="Q66" s="30"/>
-      <c r="R66" s="30"/>
-      <c r="S66" s="30"/>
-      <c r="T66" s="30"/>
-      <c r="U66" s="30"/>
-      <c r="V66" s="30"/>
+      <c r="Q66" s="31"/>
+      <c r="R66" s="31"/>
+      <c r="S66" s="31"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="31"/>
+      <c r="V66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
+      <c r="A67" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="B68" s="33">
         <v>47.42</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>38.83</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>50.6</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>73.34</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>134.67</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>66.81</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>43.03</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="33">
         <v>39.7</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="33">
         <v>55.54</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="33">
         <v>32.67</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="33">
         <v>20.93</v>
       </c>
-      <c r="M68" s="32">
+      <c r="M68" s="33">
         <v>9.97</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>7.44</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>6.94</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>9.39</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68" s="33">
         <v>11.85</v>
       </c>
-      <c r="R68" s="32">
+      <c r="R68" s="33">
         <v>12.89</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="32">
         <v>264.75</v>
       </c>
-      <c r="T68" s="30"/>
-      <c r="U68" s="30"/>
-      <c r="V68" s="30"/>
+      <c r="T68" s="31"/>
+      <c r="U68" s="31"/>
+      <c r="V68" s="31"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B69" s="33">
         <v>64.68</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>70.46</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>74.76</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>81.06</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>85.02</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>52.32</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>39.51</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="33">
         <v>34.29</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="33">
         <v>27.84</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>19.24</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>12.17</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="33">
         <v>8.92</v>
       </c>
-      <c r="N69" s="32">
+      <c r="N69" s="33">
         <v>10.1</v>
       </c>
-      <c r="O69" s="32">
+      <c r="O69" s="33">
         <v>19.15</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="33">
         <v>31.64</v>
       </c>
-      <c r="Q69" s="30"/>
-      <c r="R69" s="30"/>
-      <c r="S69" s="30"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
-      <c r="V69" s="30"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
+      <c r="A70" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="29"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="29"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="B71" s="32">
+      <c r="A71" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B71" s="33">
         <v>68.92</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="33">
         <v>58.6</v>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="33">
         <v>68.83</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="32">
         <v>107.25</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="32">
         <v>174.49</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="33">
         <v>99.95</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H71" s="33">
         <v>80.31</v>
       </c>
-      <c r="I71" s="31">
+      <c r="I71" s="32">
         <v>112.52</v>
       </c>
-      <c r="J71" s="30"/>
-      <c r="K71" s="30"/>
-      <c r="L71" s="32">
+      <c r="J71" s="31"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="33">
         <v>63.61</v>
       </c>
-      <c r="M71" s="30"/>
-      <c r="N71" s="32">
+      <c r="M71" s="31"/>
+      <c r="N71" s="33">
         <v>49.65</v>
       </c>
-      <c r="O71" s="32">
+      <c r="O71" s="33">
         <v>28.23</v>
       </c>
-      <c r="P71" s="30"/>
-      <c r="Q71" s="30"/>
-      <c r="R71" s="31">
+      <c r="P71" s="31"/>
+      <c r="Q71" s="31"/>
+      <c r="R71" s="32">
         <v>114.83</v>
       </c>
-      <c r="S71" s="30"/>
-      <c r="T71" s="30"/>
-      <c r="U71" s="30"/>
-      <c r="V71" s="30"/>
+      <c r="S71" s="31"/>
+      <c r="T71" s="31"/>
+      <c r="U71" s="31"/>
+      <c r="V71" s="31"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="B72" s="32">
+      <c r="A72" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="B72" s="33">
         <v>91.89</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="32">
         <v>100.01</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="32">
         <v>107.27</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="32">
         <v>122.04</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="32">
         <v>135.81</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="32">
         <v>124.2</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="32">
         <v>157.65</v>
       </c>
-      <c r="I72" s="30"/>
-      <c r="J72" s="30"/>
-      <c r="K72" s="30"/>
-      <c r="L72" s="32">
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="33">
         <v>99.86</v>
       </c>
-      <c r="M72" s="30"/>
-      <c r="N72" s="31">
+      <c r="M72" s="31"/>
+      <c r="N72" s="32">
         <v>467.66</v>
       </c>
-      <c r="O72" s="30"/>
-      <c r="P72" s="30"/>
-      <c r="Q72" s="30"/>
-      <c r="R72" s="30"/>
-      <c r="S72" s="30"/>
-      <c r="T72" s="30"/>
-      <c r="U72" s="30"/>
-      <c r="V72" s="30"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="31"/>
+      <c r="V72" s="31"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
